--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496520</v>
+        <v>124496468</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766599</v>
+        <v>766593</v>
       </c>
       <c r="R2" t="n">
-        <v>7078168</v>
+        <v>7078154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496468</v>
+        <v>124496815</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766593</v>
+        <v>766701</v>
       </c>
       <c r="R4" t="n">
-        <v>7078154</v>
+        <v>7078152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496815</v>
+        <v>124496520</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766701</v>
+        <v>766599</v>
       </c>
       <c r="R5" t="n">
-        <v>7078152</v>
+        <v>7078168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496468</v>
+        <v>124496520</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766593</v>
+        <v>766599</v>
       </c>
       <c r="R2" t="n">
-        <v>7078154</v>
+        <v>7078168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496585</v>
+        <v>124496468</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766610</v>
+        <v>766593</v>
       </c>
       <c r="R3" t="n">
-        <v>7078164</v>
+        <v>7078154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496520</v>
+        <v>124496585</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766599</v>
+        <v>766610</v>
       </c>
       <c r="R5" t="n">
-        <v>7078168</v>
+        <v>7078164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496520</v>
+        <v>124496585</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766599</v>
+        <v>766610</v>
       </c>
       <c r="R2" t="n">
-        <v>7078168</v>
+        <v>7078164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496585</v>
+        <v>124496520</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766610</v>
+        <v>766599</v>
       </c>
       <c r="R5" t="n">
-        <v>7078164</v>
+        <v>7078168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496815</v>
+        <v>124496520</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766701</v>
+        <v>766599</v>
       </c>
       <c r="R4" t="n">
-        <v>7078152</v>
+        <v>7078168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496520</v>
+        <v>124496815</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766599</v>
+        <v>766701</v>
       </c>
       <c r="R5" t="n">
-        <v>7078168</v>
+        <v>7078152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496585</v>
+        <v>124496815</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766610</v>
+        <v>766701</v>
       </c>
       <c r="R2" t="n">
-        <v>7078164</v>
+        <v>7078152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496468</v>
+        <v>124496520</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766593</v>
+        <v>766599</v>
       </c>
       <c r="R3" t="n">
-        <v>7078154</v>
+        <v>7078168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496520</v>
+        <v>124496585</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766599</v>
+        <v>766610</v>
       </c>
       <c r="R4" t="n">
-        <v>7078168</v>
+        <v>7078164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496815</v>
+        <v>124496468</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766701</v>
+        <v>766593</v>
       </c>
       <c r="R5" t="n">
-        <v>7078152</v>
+        <v>7078154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496815</v>
+        <v>124496585</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766701</v>
+        <v>766610</v>
       </c>
       <c r="R2" t="n">
-        <v>7078152</v>
+        <v>7078164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496520</v>
+        <v>124496468</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766599</v>
+        <v>766593</v>
       </c>
       <c r="R3" t="n">
-        <v>7078168</v>
+        <v>7078154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496585</v>
+        <v>124496520</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766610</v>
+        <v>766599</v>
       </c>
       <c r="R4" t="n">
-        <v>7078164</v>
+        <v>7078168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496468</v>
+        <v>124496815</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766593</v>
+        <v>766701</v>
       </c>
       <c r="R5" t="n">
-        <v>7078154</v>
+        <v>7078152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496468</v>
+        <v>124496520</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766593</v>
+        <v>766599</v>
       </c>
       <c r="R3" t="n">
-        <v>7078154</v>
+        <v>7078168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496520</v>
+        <v>124496468</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766599</v>
+        <v>766593</v>
       </c>
       <c r="R4" t="n">
-        <v>7078168</v>
+        <v>7078154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496585</v>
+        <v>124496520</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766610</v>
+        <v>766599</v>
       </c>
       <c r="R2" t="n">
-        <v>7078164</v>
+        <v>7078168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496520</v>
+        <v>124496815</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766599</v>
+        <v>766701</v>
       </c>
       <c r="R3" t="n">
-        <v>7078168</v>
+        <v>7078152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496468</v>
+        <v>124496585</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766593</v>
+        <v>766610</v>
       </c>
       <c r="R4" t="n">
-        <v>7078154</v>
+        <v>7078164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496815</v>
+        <v>124496468</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766701</v>
+        <v>766593</v>
       </c>
       <c r="R5" t="n">
-        <v>7078152</v>
+        <v>7078154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496585</v>
+        <v>124496468</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766610</v>
+        <v>766593</v>
       </c>
       <c r="R4" t="n">
-        <v>7078164</v>
+        <v>7078154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496468</v>
+        <v>124496585</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766593</v>
+        <v>766610</v>
       </c>
       <c r="R5" t="n">
-        <v>7078154</v>
+        <v>7078164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496520</v>
+        <v>124496815</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766599</v>
+        <v>766701</v>
       </c>
       <c r="R2" t="n">
-        <v>7078168</v>
+        <v>7078152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496815</v>
+        <v>124496585</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766701</v>
+        <v>766610</v>
       </c>
       <c r="R3" t="n">
-        <v>7078152</v>
+        <v>7078164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496468</v>
+        <v>124496520</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766593</v>
+        <v>766599</v>
       </c>
       <c r="R4" t="n">
-        <v>7078154</v>
+        <v>7078168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496585</v>
+        <v>124496468</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766610</v>
+        <v>766593</v>
       </c>
       <c r="R5" t="n">
-        <v>7078164</v>
+        <v>7078154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496815</v>
+        <v>124496520</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766701</v>
+        <v>766599</v>
       </c>
       <c r="R2" t="n">
-        <v>7078152</v>
+        <v>7078168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496585</v>
+        <v>124496815</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766610</v>
+        <v>766701</v>
       </c>
       <c r="R3" t="n">
-        <v>7078164</v>
+        <v>7078152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496520</v>
+        <v>124496468</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766599</v>
+        <v>766593</v>
       </c>
       <c r="R4" t="n">
-        <v>7078168</v>
+        <v>7078154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496468</v>
+        <v>124496585</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766593</v>
+        <v>766610</v>
       </c>
       <c r="R5" t="n">
-        <v>7078154</v>
+        <v>7078164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496520</v>
+        <v>124496815</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766599</v>
+        <v>766701</v>
       </c>
       <c r="R2" t="n">
-        <v>7078168</v>
+        <v>7078152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496815</v>
+        <v>124496468</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766701</v>
+        <v>766593</v>
       </c>
       <c r="R3" t="n">
-        <v>7078152</v>
+        <v>7078154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496468</v>
+        <v>124496520</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766593</v>
+        <v>766599</v>
       </c>
       <c r="R4" t="n">
-        <v>7078154</v>
+        <v>7078168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496815</v>
+        <v>124496520</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766701</v>
+        <v>766599</v>
       </c>
       <c r="R2" t="n">
-        <v>7078152</v>
+        <v>7078168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496468</v>
+        <v>124496815</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766593</v>
+        <v>766701</v>
       </c>
       <c r="R3" t="n">
-        <v>7078154</v>
+        <v>7078152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496520</v>
+        <v>124496468</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766599</v>
+        <v>766593</v>
       </c>
       <c r="R4" t="n">
-        <v>7078168</v>
+        <v>7078154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496815</v>
+        <v>124496468</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766701</v>
+        <v>766593</v>
       </c>
       <c r="R3" t="n">
-        <v>7078152</v>
+        <v>7078154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496468</v>
+        <v>124496815</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766593</v>
+        <v>766701</v>
       </c>
       <c r="R4" t="n">
-        <v>7078154</v>
+        <v>7078152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496815</v>
+        <v>124496585</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766701</v>
+        <v>766610</v>
       </c>
       <c r="R4" t="n">
-        <v>7078152</v>
+        <v>7078164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496585</v>
+        <v>124496815</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766610</v>
+        <v>766701</v>
       </c>
       <c r="R5" t="n">
-        <v>7078164</v>
+        <v>7078152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496520</v>
+        <v>124496468</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766599</v>
+        <v>766593</v>
       </c>
       <c r="R2" t="n">
-        <v>7078168</v>
+        <v>7078154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496468</v>
+        <v>124496585</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766593</v>
+        <v>766610</v>
       </c>
       <c r="R3" t="n">
-        <v>7078154</v>
+        <v>7078164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496585</v>
+        <v>124496815</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766610</v>
+        <v>766701</v>
       </c>
       <c r="R4" t="n">
-        <v>7078164</v>
+        <v>7078152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124496815</v>
+        <v>124496520</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766701</v>
+        <v>766599</v>
       </c>
       <c r="R5" t="n">
-        <v>7078152</v>
+        <v>7078168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124496468</v>
+        <v>124496585</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766593</v>
+        <v>766610</v>
       </c>
       <c r="R2" t="n">
-        <v>7078154</v>
+        <v>7078164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124496585</v>
+        <v>124496520</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766610</v>
+        <v>766599</v>
       </c>
       <c r="R3" t="n">
-        <v>7078164</v>
+        <v>7078168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124496815</v>
+        <v>124496468</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766701</v>
+        <v>766593</v>
       </c>
       <c r="R4" t="n">
-        <v>7078152</v>
+        <v>7078154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,108 +963,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>124496520</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kasaviken, Kasaviken, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>766599</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7078168</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5029-2022 artfynd.xlsx
+++ b/artfynd/A 5029-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124496585</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124496520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124496468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>